--- a/output/graficos_dimensiones/comunal_e_mat_a_2018_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2018_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:37</t>
+    <t xml:space="preserve">2026-09-10 00:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2018_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2018_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:45</t>
+    <t xml:space="preserve">2026-09-18 10:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2018_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2018_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:55</t>
+    <t xml:space="preserve">2026-09-23 14:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2018_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2018_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 14:14</t>
+    <t xml:space="preserve">2026-10-02 15:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2018_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2018_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:01</t>
+    <t xml:space="preserve">2026-10-04 09:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2018_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2018_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 09:57</t>
+    <t xml:space="preserve">2026-10-05 13:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -762,7 +762,7 @@
         <v>2018</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>74.39</v>
+        <v>74.4</v>
       </c>
     </row>
     <row r="13">
